--- a/forms/trg/Formulir_TRG_hes.xlsx
+++ b/forms/trg/Formulir_TRG_hes.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B21)</f>
+        <f>COUNTA(Anggota!B5:B23)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F21)</f>
+        <f>COUNTA(Anggota!F5:F23)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,14 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ir. Megasari Kurnia, S.T., M.T.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+          <t>Dr. Eng. Ir. Ilham Bakri, S.T., M.Sc., IPM</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Biopotential</t>
+          <t>Ergonomics and Occupational Safety</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,7 +929,11 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>50460964800</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,22 +946,18 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Ir. Nadzirah Ikasari S, S.T., M.T.</t>
+          <t>Prof. Satoshi Muraki, Ph.D., CPE</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Engineering Management</t>
+          <t>Human Life Design and Science</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +979,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ir. Retnari Dian Mudistuti, ST., M.Si.</t>
+          <t>Ir. Megasari Kurnia, S.T., M.T.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,7 +994,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Cognitive Ergonomics</t>
+          <t>Biopotential</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,12 +1016,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Putri Indah Wardani, S.T., M.T.</t>
+          <t>Ir. Nadzirah Ikasari S, S.T., M.T.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1039,7 +1031,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Ergonomics</t>
+          <t>Engineering Management</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,12 +1053,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Abdul Salam, S.T.</t>
+          <t>Ir. Retnari Dian Mudistuti, ST., M.Si.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1074,7 +1066,11 @@
           <t>Universitas Hasanuddin</t>
         </is>
       </c>
-      <c r="E9" s="11" t="n"/>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Cognitive Ergonomics</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1092,10 +1088,26 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="11" t="n"/>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Putri Indah Wardani, S.T., M.T.</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Ergonomics</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1103,16 +1115,36 @@
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Abdul Salam, S.T.</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>The HES Research Group focuses on integrating human factors and ergonomics into engineering design to enhance health, safety, and well-being. Through collaborative research, innovation, and education, we develop ergonomic solutions for products, workspaces, and living environments, ensuring inclusivity and comfort for all ages and abilities.</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1120,7 +1152,11 @@
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1292,15 +1328,49 @@
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="12" t="n"/>
     </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_hes.xlsx
+++ b/forms/trg/Formulir_TRG_hes.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. Eng. Ir. Ilham Bakri, S.T., M.Sc., IPM</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
